--- a/resources/TradingSystem.xlsx
+++ b/resources/TradingSystem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IN57KC\data\Projekte\Godot\PirateGame\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87FE297-D0C5-4563-AB6B-CC4C91529076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B375E7AF-3D1D-4B82-96A7-89236AABEE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{071AB512-0C26-4FD2-8186-9B19B8500D43}"/>
   </bookViews>
@@ -459,43 +459,43 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,43 +1040,43 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>7.5</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f>IF(INT($D$1*$F$1/MAX(A2,1))&gt;$D$1*3,$D$1*3,IF(INT($D$1*$F$1/MAX(A2,1))&lt;$D$1*0.5,$D$1*0.5,INT($D$1*$F$1/MAX(A2,1))))</f>
+        <f>MIN($D$1*3,MAX(INT($D$1*0.5),INT($D$1*$F$1/MAX(A2,1))))</f>
         <v>45</v>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B66" si="0">IF(INT($D$1*$F$1/MAX(A3,1))&gt;$D$1*3,$D$1*3,IF(INT($D$1*$F$1/MAX(A3,1))&lt;$D$1*0.5,$D$1*0.5,INT($D$1*$F$1/MAX(A3,1))))</f>
+        <f t="shared" ref="B3:B52" si="0">MIN($D$1*3,MAX(INT($D$1*0.5),INT($D$1*$F$1/MAX(A3,1))))</f>
         <v>45</v>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
